--- a/data/trans_bre/P20B-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P20B-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-37,19; 13,56</t>
+          <t>-34,9; 13,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-25,14; 8,75</t>
+          <t>-25,42; 9,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-39,83; 3,03</t>
+          <t>-42,62; 1,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-28,84; 9,23</t>
+          <t>-24,98; 10,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-70,78; 91,63</t>
+          <t>-70,59; 86,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-59,64; 40,06</t>
+          <t>-58,04; 42,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-67,9; 8,21</t>
+          <t>-70,91; 3,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-60,05; 34,94</t>
+          <t>-57,24; 44,42</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-24,76; 5,75</t>
+          <t>-23,31; 6,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,56; 17,06</t>
+          <t>-13,58; 16,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-22,94; 8,66</t>
+          <t>-23,41; 10,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-20,03; 12,44</t>
+          <t>-19,18; 13,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-76,15; 57,3</t>
+          <t>-72,3; 69,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-35,5; 115,39</t>
+          <t>-39,79; 107,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-62,0; 58,25</t>
+          <t>-64,63; 72,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-57,1; 81,89</t>
+          <t>-56,31; 93,93</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,46; 24,37</t>
+          <t>-9,86; 26,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-31,58; 5,82</t>
+          <t>-28,07; 8,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-32,23; 10,99</t>
+          <t>-31,69; 11,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-41,48; -3,24</t>
+          <t>-40,68; -2,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-33,96; 200,91</t>
+          <t>-37,22; 201,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-66,52; 31,04</t>
+          <t>-64,81; 42,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-66,66; 62,37</t>
+          <t>-68,77; 65,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-77,49; -6,96</t>
+          <t>-79,29; -8,99</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-29,3; 3,3</t>
+          <t>-31,03; 1,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-23,23; 7,35</t>
+          <t>-21,42; 7,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-18,8; 13,37</t>
+          <t>-18,05; 14,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-21,59; 5,23</t>
+          <t>-21,69; 4,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-72,02; 16,83</t>
+          <t>-73,27; 9,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-61,16; 37,96</t>
+          <t>-57,38; 45,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-49,8; 77,99</t>
+          <t>-49,79; 90,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-53,19; 20,9</t>
+          <t>-53,74; 15,93</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-14,98; 1,92</t>
+          <t>-14,9; 2,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,37; 2,97</t>
+          <t>-13,11; 3,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-19,16; 0,05</t>
+          <t>-18,99; 0,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-18,67; -1,36</t>
+          <t>-18,38; -2,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-47,18; 10,86</t>
+          <t>-47,18; 13,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-38,75; 12,51</t>
+          <t>-37,91; 13,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-47,92; 0,31</t>
+          <t>-48,1; 2,99</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-49,23; -4,93</t>
+          <t>-47,82; -6,54</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P20B-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P20B-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-8,7</t>
+          <t>-6,35</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-24,11%</t>
+          <t>-18,27%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-34,9; 13,25</t>
+          <t>-37,93; 11,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-25,42; 9,16</t>
+          <t>-24,89; 8,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-42,62; 1,18</t>
+          <t>-42,57; 0,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-24,98; 10,65</t>
+          <t>-25,29; 10,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-70,59; 86,61</t>
+          <t>-70,5; 87,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-58,04; 42,62</t>
+          <t>-58,33; 45,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-70,91; 3,49</t>
+          <t>-69,18; 2,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-57,24; 44,42</t>
+          <t>-55,67; 40,85</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-4,03</t>
+          <t>-6,49</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-15,56%</t>
+          <t>-22,65%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-23,31; 6,58</t>
+          <t>-22,99; 7,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-13,58; 16,86</t>
+          <t>-15,79; 16,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-23,41; 10,09</t>
+          <t>-22,79; 9,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-19,18; 13,59</t>
+          <t>-22,1; 11,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-72,3; 69,08</t>
+          <t>-73,24; 73,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-39,79; 107,0</t>
+          <t>-43,06; 104,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-64,63; 72,06</t>
+          <t>-63,18; 66,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-56,31; 93,93</t>
+          <t>-58,4; 72,38</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-22,15</t>
+          <t>-22,16</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-55,22%</t>
+          <t>-54,55%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,86; 26,28</t>
+          <t>-13,04; 23,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-28,07; 8,2</t>
+          <t>-29,66; 7,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-31,69; 11,97</t>
+          <t>-29,65; 11,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-40,68; -2,67</t>
+          <t>-41,67; -4,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-37,22; 201,04</t>
+          <t>-39,77; 216,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-64,81; 42,12</t>
+          <t>-65,36; 39,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-68,77; 65,05</t>
+          <t>-63,63; 66,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-79,29; -8,99</t>
+          <t>-75,63; -9,47</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-8,43</t>
+          <t>-7,22</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-25,9%</t>
+          <t>-22,81%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-31,03; 1,38</t>
+          <t>-30,88; 1,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-21,42; 7,96</t>
+          <t>-20,9; 8,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-18,05; 14,49</t>
+          <t>-20,1; 13,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-21,69; 4,07</t>
+          <t>-20,39; 4,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-73,27; 9,53</t>
+          <t>-73,87; 17,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-57,38; 45,06</t>
+          <t>-57,23; 61,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-49,79; 90,56</t>
+          <t>-54,11; 76,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-53,74; 15,93</t>
+          <t>-50,68; 18,73</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-10,13</t>
+          <t>-9,9</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-30,59%</t>
+          <t>-29,79%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-14,9; 2,69</t>
+          <t>-14,99; 2,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,11; 3,2</t>
+          <t>-13,55; 3,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-18,99; 0,61</t>
+          <t>-18,67; -0,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-18,38; -2,41</t>
+          <t>-18,05; -1,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-47,18; 13,67</t>
+          <t>-47,19; 14,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-37,91; 13,89</t>
+          <t>-39,16; 15,21</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-48,1; 2,99</t>
+          <t>-46,47; -0,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-47,82; -6,54</t>
+          <t>-47,21; -3,06</t>
         </is>
       </c>
     </row>
